--- a/final_outputs/excel_tables/table_qr_full.xlsx
+++ b/final_outputs/excel_tables/table_qr_full.xlsx
@@ -493,52 +493,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>-0.000009</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.000035, 0.000000]</t>
+          <t>[-0.000027, 0.000010]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.000018*</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[-0.000033, -0.000002]</t>
+          <t>[-0.000026, 0.000006]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.000014*</t>
+          <t>-0.000011</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[-0.000027, -0.000001]</t>
+          <t>[-0.000024, 0.000005]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>-0.000003</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[-0.000020, 0.000003]</t>
+          <t>[-0.000016, 0.000010]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.000005</t>
+          <t>0.000007</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[-0.000024, 0.000012]</t>
+          <t>[-0.000016, 0.000039]</t>
         </is>
       </c>
     </row>
@@ -550,52 +550,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.000238</t>
+          <t>0.000727</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.000307, 0.000791]</t>
+          <t>[-0.000024, 0.001417]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.000334</t>
+          <t>0.000488</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[-0.000120, 0.000808]</t>
+          <t>[-0.000013, 0.001046]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000280</t>
+          <t>0.000352*</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[-0.000115, 0.000641]</t>
+          <t>[0.000005, 0.000764]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.000401*</t>
+          <t>0.000509*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.000046, 0.000745]</t>
+          <t>[0.000148, 0.000923]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.000299</t>
+          <t>0.000520</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[-0.000221, 0.000761]</t>
+          <t>[-0.000005, 0.001501]</t>
         </is>
       </c>
     </row>
@@ -607,52 +607,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.000169</t>
+          <t>0.000361</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[-0.000487, 0.000641]</t>
+          <t>[-0.000244, 0.001097]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.000092</t>
+          <t>0.000064</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[-0.000514, 0.000314]</t>
+          <t>[-0.000401, 0.000547]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.000196</t>
+          <t>-0.000112</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[-0.000466, 0.000104]</t>
+          <t>[-0.000435, 0.000193]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.000245</t>
+          <t>-0.000047</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[-0.000745, 0.000077]</t>
+          <t>[-0.000717, 0.000295]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.000453</t>
+          <t>-0.000064</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[-0.001156, 0.000033]</t>
+          <t>[-0.001096, 0.001167]</t>
         </is>
       </c>
     </row>
@@ -664,52 +664,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.000567</t>
+          <t>0.000230</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[-0.002567, 0.000707]</t>
+          <t>[-0.002190, 0.001796]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.000946*</t>
+          <t>-0.000758</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[-0.001669, -0.000037]</t>
+          <t>[-0.001367, 0.000669]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.000793*</t>
+          <t>-0.000580</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[-0.001458, -0.000161]</t>
+          <t>[-0.001296, 0.000209]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.001257*</t>
+          <t>-0.000745</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[-0.002014, -0.000260]</t>
+          <t>[-0.001758, 0.000646]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.001728*</t>
+          <t>-0.000598</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[-0.002576, -0.000046]</t>
+          <t>[-0.002110, 0.002208]</t>
         </is>
       </c>
     </row>
@@ -721,52 +721,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.000639</t>
+          <t>0.000055</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[-0.000614, 0.001271]</t>
+          <t>[-0.001013, 0.001057]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.000354</t>
+          <t>0.000303</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[-0.000397, 0.000914]</t>
+          <t>[-0.000488, 0.000897]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.000010</t>
+          <t>-0.000130</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.000429, 0.000465]</t>
+          <t>[-0.000523, 0.000373]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.000025</t>
+          <t>-0.000080</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[-0.000428, 0.000530]</t>
+          <t>[-0.000575, 0.000461]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.000084</t>
+          <t>0.000098</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[-0.000459, 0.000915]</t>
+          <t>[-0.001180, 0.000714]</t>
         </is>
       </c>
     </row>

--- a/final_outputs/excel_tables/table_qr_full.xlsx
+++ b/final_outputs/excel_tables/table_qr_full.xlsx
@@ -493,52 +493,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>-0.000020*</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[-0.000044, -0.000002]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-0.000020*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[-0.000036, -0.000005]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-0.000016*</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[-0.000030, -0.000003]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.000012</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[-0.000027, 0.000000]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>-0.000009</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[-0.000027, 0.000010]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-0.000012</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[-0.000026, 0.000006]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-0.000011</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[-0.000024, 0.000005]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.000003</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>[-0.000016, 0.000010]</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.000007</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[-0.000016, 0.000039]</t>
+          <t>[-0.000032, 0.000008]</t>
         </is>
       </c>
     </row>
@@ -550,52 +550,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.000727</t>
+          <t>0.000033</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.000024, 0.001417]</t>
+          <t>[-0.000582, 0.000760]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.000488</t>
+          <t>0.000313</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[-0.000013, 0.001046]</t>
+          <t>[-0.000187, 0.000760]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000352*</t>
+          <t>0.000206</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.000005, 0.000764]</t>
+          <t>[-0.000160, 0.000620]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.000509*</t>
+          <t>0.000298</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.000148, 0.000923]</t>
+          <t>[-0.000110, 0.000695]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.000520</t>
+          <t>0.000153</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[-0.000005, 0.001501]</t>
+          <t>[-0.000478, 0.000640]</t>
         </is>
       </c>
     </row>
@@ -607,52 +607,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.000361</t>
+          <t>-0.000563</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[-0.000244, 0.001097]</t>
+          <t>[-0.001915, 0.000531]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.000064</t>
+          <t>-0.000277</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[-0.000401, 0.000547]</t>
+          <t>[-0.000899, 0.000087]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.000112</t>
+          <t>-0.000348</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[-0.000435, 0.000193]</t>
+          <t>[-0.000722, 0.000016]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.000047</t>
+          <t>-0.000526*</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[-0.000717, 0.000295]</t>
+          <t>[-0.001143, -0.000030]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.000064</t>
+          <t>-0.000931*</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[-0.001096, 0.001167]</t>
+          <t>[-0.001850, -0.000257]</t>
         </is>
       </c>
     </row>
@@ -664,52 +664,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.000230</t>
+          <t>-0.002339</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[-0.002190, 0.001796]</t>
+          <t>[-0.004545, 0.000192]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.000758</t>
+          <t>-0.001350*</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[-0.001367, 0.000669]</t>
+          <t>[-0.002590, -0.000550]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.000580</t>
+          <t>-0.001138*</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[-0.001296, 0.000209]</t>
+          <t>[-0.002023, -0.000458]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.000745</t>
+          <t>-0.001760*</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[-0.001758, 0.000646]</t>
+          <t>[-0.002694, -0.000695]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.000598</t>
+          <t>-0.002560*</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[-0.002110, 0.002208]</t>
+          <t>[-0.003982, -0.000946]</t>
         </is>
       </c>
     </row>
@@ -721,52 +721,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.000055</t>
+          <t>0.001124</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[-0.001013, 0.001057]</t>
+          <t>[-0.000411, 0.001996]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.000303</t>
+          <t>0.000481</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[-0.000488, 0.000897]</t>
+          <t>[-0.000343, 0.001108]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.000130</t>
+          <t>0.000162</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.000523, 0.000373]</t>
+          <t>[-0.000348, 0.000610]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.000080</t>
+          <t>0.000187</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[-0.000575, 0.000461]</t>
+          <t>[-0.000403, 0.000710]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.000098</t>
+          <t>0.000329</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[-0.001180, 0.000714]</t>
+          <t>[-0.000354, 0.001088]</t>
         </is>
       </c>
     </row>
